--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.95177648574678</v>
+        <v>5.517163678933852</v>
       </c>
       <c r="D2" t="n">
-        <v>33.47835780678252</v>
+        <v>5.44023314360216</v>
       </c>
       <c r="E2" t="n">
-        <v>8.344280325754182</v>
+        <v>1.355945552935055</v>
       </c>
       <c r="F2" t="n">
-        <v>8.818059918650317</v>
+        <v>1.432934736780676</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.26321583423842</v>
+        <v>2.805272573063743</v>
       </c>
       <c r="D3" t="n">
-        <v>51.11447764408315</v>
+        <v>8.306102617163512</v>
       </c>
       <c r="E3" t="n">
-        <v>8.344280325754182</v>
+        <v>1.355945552935055</v>
       </c>
       <c r="F3" t="n">
-        <v>8.818059918650317</v>
+        <v>1.432934736780676</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
